--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Deakin\MIS 770 Foundation Skill In data Analytics\ASS 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42DB1F3A-B451-47A4-9DF7-E7BFB72E66C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98124DFF-F724-427E-8088-CA2E46E7F728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{2824816B-C331-4A54-9855-309D81916BF8}"/>
   </bookViews>
@@ -186,7 +186,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FAD50EE6-CD41-49D2-BC42-2732F0FAF825}" name="Table1" displayName="Table1" ref="A1:Q216" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:Q216" xr:uid="{FAD50EE6-CD41-49D2-BC42-2732F0FAF825}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{018C4C78-03F5-45FB-B37D-DC53E601B4DB}" name="Salary"/>
     <tableColumn id="2" xr3:uid="{A574B365-A92F-49D1-A57D-DA4475C1DC1A}" name="Gender"/>
